--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 8,06</t>
+          <t>-13,61; 9,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 3,98</t>
+          <t>-21,16; 2,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -41,13</t>
+          <t>-57,95; -41,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 10,96</t>
+          <t>-7,68; 12,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,9; -5,76</t>
+          <t>-26,05; -4,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,38; -52,59</t>
+          <t>-69,06; -53,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 7,42</t>
+          <t>-8,22; 6,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,04; -3,73</t>
+          <t>-19,91; -4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-61,82; -50,38</t>
+          <t>-61,54; -50,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 16,56</t>
+          <t>-22,88; 19,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 8,7</t>
+          <t>-34,79; 5,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,3; -87,39</t>
+          <t>-96,39; -88,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 18,24</t>
+          <t>-10,85; 20,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,2; -9,68</t>
+          <t>-36,9; -7,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,23; -89,19</t>
+          <t>-95,21; -89,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 13,32</t>
+          <t>-13,12; 12,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,58; -7,06</t>
+          <t>-31,2; -8,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,12; -90,34</t>
+          <t>-94,98; -90,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 22,0</t>
+          <t>5,95; 21,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 18,79</t>
+          <t>2,22; 18,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,26; -16,48</t>
+          <t>-28,78; -16,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 26,96</t>
+          <t>12,64; 26,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 15,86</t>
+          <t>0,06; 14,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,8; -22,23</t>
+          <t>-33,62; -21,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 21,62</t>
+          <t>11,34; 22,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 14,53</t>
+          <t>3,72; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,24; -21,89</t>
+          <t>-30,33; -21,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 92,8</t>
+          <t>16,99; 89,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 74,89</t>
+          <t>6,09; 78,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,89; -69,85</t>
+          <t>-87,66; -68,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,11; 73,94</t>
+          <t>29,27; 73,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 43,97</t>
+          <t>0,29; 40,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,24; -60,59</t>
+          <t>-75,85; -60,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,62; 66,34</t>
+          <t>30,27; 70,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 45,64</t>
+          <t>9,67; 46,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-79,65; -68,5</t>
+          <t>-79,73; -67,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 22,03</t>
+          <t>1,98; 22,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 9,08</t>
+          <t>-11,08; 8,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,49; -26,37</t>
+          <t>-41,8; -26,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 21,39</t>
+          <t>1,76; 20,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 4,59</t>
+          <t>-15,31; 4,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,21; -34,42</t>
+          <t>-48,55; -34,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 17,99</t>
+          <t>4,87; 18,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,73</t>
+          <t>-10,4; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-43,45; -33,36</t>
+          <t>-43,15; -33,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 66,59</t>
+          <t>3,91; 63,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 27,37</t>
+          <t>-25,02; 26,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,45; -78,19</t>
+          <t>-91,23; -77,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 50,78</t>
+          <t>3,17; 47,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 10,29</t>
+          <t>-29,16; 8,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,95; -79,38</t>
+          <t>-90,28; -79,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 44,03</t>
+          <t>10,8; 47,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 9,16</t>
+          <t>-21,57; 8,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,31; -81,46</t>
+          <t>-89,23; -81,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 11,65</t>
+          <t>-8,22; 11,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -1,44</t>
+          <t>-21,98; -1,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -29,27</t>
+          <t>-44,64; -29,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 21,09</t>
+          <t>4,36; 21,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 8,76</t>
+          <t>-9,54; 8,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,04; -32,1</t>
+          <t>-47,25; -32,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,26</t>
+          <t>1,71; 14,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 0,92</t>
+          <t>-12,56; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-43,9; -33,21</t>
+          <t>-44,34; -32,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 29,74</t>
+          <t>-15,99; 28,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,59; -3,49</t>
+          <t>-43,47; -3,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,8; -70,34</t>
+          <t>-88,29; -70,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 46,85</t>
+          <t>8,37; 48,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 19,24</t>
+          <t>-17,59; 18,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,94; -71,43</t>
+          <t>-87,74; -71,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 32,08</t>
+          <t>3,19; 32,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 1,86</t>
+          <t>-24,39; 3,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,07; -74,14</t>
+          <t>-86,47; -74,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 21,21</t>
+          <t>-3,35; 20,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,93; 39,54</t>
+          <t>15,77; 40,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -11,95</t>
+          <t>-31,1; -11,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 31,94</t>
+          <t>9,19; 31,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,68; 35,87</t>
+          <t>12,57; 35,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -23,8</t>
+          <t>-40,77; -23,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,78; 23,83</t>
+          <t>6,68; 23,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,22; 34,63</t>
+          <t>18,0; 34,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-34,04; -20,87</t>
+          <t>-33,77; -21,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 88,48</t>
+          <t>-9,56; 90,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>45,48; 169,18</t>
+          <t>42,79; 179,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,01; -51,03</t>
+          <t>-84,42; -49,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24,58; 111,89</t>
+          <t>21,09; 102,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,66; 124,33</t>
+          <t>30,19; 120,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-93,13; -78,31</t>
+          <t>-93,74; -77,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,56; 84,6</t>
+          <t>17,31; 80,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>50,97; 124,6</t>
+          <t>48,12; 123,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-88,99; -73,87</t>
+          <t>-88,01; -72,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 18,25</t>
+          <t>-3,27; 18,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 7,46</t>
+          <t>-13,68; 7,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -22,97</t>
+          <t>-39,67; -22,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,62; 27,41</t>
+          <t>7,08; 28,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 11,72</t>
+          <t>-9,2; 11,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-36,54; -20,3</t>
+          <t>-36,39; -19,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,2; 20,02</t>
+          <t>4,35; 19,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,77</t>
+          <t>-8,58; 6,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-36,31; -24,21</t>
+          <t>-36,03; -24,08</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 49,0</t>
+          <t>-6,72; 49,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 20,37</t>
+          <t>-28,31; 19,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,78; -64,04</t>
+          <t>-81,78; -61,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14,75; 79,25</t>
+          <t>15,22; 83,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 32,99</t>
+          <t>-20,58; 32,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,7; -57,34</t>
+          <t>-78,44; -56,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,33; 52,75</t>
+          <t>9,23; 52,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 17,67</t>
+          <t>-18,74; 17,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,49; -64,32</t>
+          <t>-78,24; -63,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>18,86; 32,76</t>
+          <t>18,3; 33,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 15,2</t>
+          <t>-1,05; 14,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-36,77; -26,22</t>
+          <t>-36,86; -26,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,55; 19,12</t>
+          <t>5,9; 19,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,0</t>
+          <t>-8,49; 4,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 8,32</t>
+          <t>-49,69; 12,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,53; 23,43</t>
+          <t>13,73; 23,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 7,52</t>
+          <t>-2,71; 7,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 5,31</t>
+          <t>-41,88; 2,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>49,58; 106,4</t>
+          <t>46,33; 108,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,39; 49,23</t>
+          <t>-2,07; 47,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-94,77; -84,96</t>
+          <t>-94,94; -85,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,67; 39,23</t>
+          <t>10,3; 39,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 10,14</t>
+          <t>-15,42; 9,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-92,68; 16,93</t>
+          <t>-92,85; 24,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,23; 57,88</t>
+          <t>29,69; 56,6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 17,95</t>
+          <t>-5,7; 17,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,54; 11,87</t>
+          <t>-92,6; 5,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,08; 19,73</t>
+          <t>6,23; 19,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,28</t>
+          <t>12,37; 25,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,24; -13,8</t>
+          <t>-29,78; -13,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,9; 26,51</t>
+          <t>14,6; 26,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,2; 24,17</t>
+          <t>11,55; 23,69</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -9,13</t>
+          <t>-19,17; -9,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,38; 21,79</t>
+          <t>12,97; 21,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14,16; 22,65</t>
+          <t>14,22; 22,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-25,95; -13,84</t>
+          <t>-26,49; -13,54</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,37; 66,28</t>
+          <t>16,46; 63,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>34,95; 87,6</t>
+          <t>33,92; 87,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,49; -43,73</t>
+          <t>-82,67; -43,61</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33,38; 70,27</t>
+          <t>32,47; 71,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>27,57; 64,29</t>
+          <t>26,47; 63,2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,44; -24,31</t>
+          <t>-43,46; -24,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,36; 62,95</t>
+          <t>32,54; 61,58</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>36,0; 65,03</t>
+          <t>35,66; 66,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-69,11; -38,42</t>
+          <t>-68,32; -37,5</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,35</t>
+          <t>9,39; 15,38</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,25</t>
+          <t>4,17; 10,35</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -26,61</t>
+          <t>-31,87; -26,56</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,71</t>
+          <t>12,66; 18,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,1</t>
+          <t>1,98; 8,07</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-35,15; -13,5</t>
+          <t>-34,97; -13,19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,22</t>
+          <t>12,01; 16,18</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,7</t>
+          <t>3,73; 8,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -19,94</t>
+          <t>-32,76; -21,31</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>24,91; 43,07</t>
+          <t>24,23; 43,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,66; 29,1</t>
+          <t>10,93; 28,89</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -75,76</t>
+          <t>-83,61; -75,7</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27,3; 42,07</t>
+          <t>26,64; 41,24</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,33; 17,99</t>
+          <t>4,12; 18,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-75,41; -29,28</t>
+          <t>-75,25; -29,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>27,07; 40,0</t>
+          <t>28,2; 40,1</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,24</t>
+          <t>8,52; 20,02</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-77,62; -48,08</t>
+          <t>-77,41; -50,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-49,68</t>
+          <t>-49,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-61,03</t>
+          <t>-60,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-55,76</t>
+          <t>-55,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 9,0</t>
+          <t>-14,67; 8,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 2,51</t>
+          <t>-19,35; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-57,95; -41,29</t>
+          <t>-58,48; -41,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 12,45</t>
+          <t>-9,13; 12,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -4,73</t>
+          <t>-25,07; -3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,06; -53,4</t>
+          <t>-67,29; -52,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 6,95</t>
+          <t>-7,95; 7,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -4,67</t>
+          <t>-19,2; -3,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-61,54; -50,09</t>
+          <t>-61,22; -49,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-93,13%</t>
+          <t>-93,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-92,69%</t>
+          <t>-91,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-92,97%</t>
+          <t>-92,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 19,29</t>
+          <t>-24,58; 18,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 5,33</t>
+          <t>-33,2; 6,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,39; -88,13</t>
+          <t>-96,41; -88,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 20,71</t>
+          <t>-12,69; 19,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,9; -7,57</t>
+          <t>-35,29; -5,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,21; -89,02</t>
+          <t>-94,37; -88,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 12,48</t>
+          <t>-12,36; 12,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -8,05</t>
+          <t>-30,49; -5,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,98; -90,19</t>
+          <t>-94,54; -89,74</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-22,84</t>
+          <t>-21,82</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-27,93</t>
+          <t>-27,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-26,03</t>
+          <t>-25,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 21,7</t>
+          <t>5,63; 21,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 18,76</t>
+          <t>1,78; 17,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,78; -16,66</t>
+          <t>-28,17; -16,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,64; 26,8</t>
+          <t>12,56; 26,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 14,93</t>
+          <t>0,26; 15,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,62; -21,87</t>
+          <t>-33,4; -21,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 22,32</t>
+          <t>10,76; 21,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,85</t>
+          <t>2,59; 14,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-30,33; -21,83</t>
+          <t>-29,67; -21,45</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-80,51%</t>
+          <t>-76,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-69,26%</t>
+          <t>-67,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-74,41%</t>
+          <t>-71,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 89,35</t>
+          <t>17,35; 86,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 78,59</t>
+          <t>5,15; 71,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,66; -68,95</t>
+          <t>-85,07; -65,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 73,73</t>
+          <t>28,3; 73,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 40,36</t>
+          <t>0,27; 41,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,85; -60,52</t>
+          <t>-74,62; -57,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,27; 70,45</t>
+          <t>27,86; 66,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 46,74</t>
+          <t>6,89; 45,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-79,73; -67,78</t>
+          <t>-77,51; -65,84</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-34,25</t>
+          <t>-33,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,37</t>
+          <t>-41,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-38,14</t>
+          <t>-38,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 22,39</t>
+          <t>3,16; 22,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 8,65</t>
+          <t>-11,4; 9,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -26,83</t>
+          <t>-41,52; -26,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 20,18</t>
+          <t>1,14; 19,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 4,12</t>
+          <t>-14,56; 3,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,55; -34,3</t>
+          <t>-48,34; -34,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 18,71</t>
+          <t>4,82; 18,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 3,65</t>
+          <t>-10,1; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-43,15; -33,17</t>
+          <t>-43,32; -32,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-86,33%</t>
+          <t>-85,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-85,67%</t>
+          <t>-86,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-86,0%</t>
+          <t>-85,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 63,7</t>
+          <t>6,8; 64,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 26,46</t>
+          <t>-24,96; 26,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,23; -77,95</t>
+          <t>-91,36; -77,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 47,45</t>
+          <t>2,12; 45,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 8,96</t>
+          <t>-28,1; 7,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,28; -79,8</t>
+          <t>-90,58; -80,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 47,32</t>
+          <t>9,87; 46,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 8,7</t>
+          <t>-21,11; 8,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,23; -81,21</t>
+          <t>-89,28; -81,4</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-37,79</t>
+          <t>-37,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-39,09</t>
+          <t>-35,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-38,43</t>
+          <t>-36,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 11,7</t>
+          <t>-7,61; 11,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -1,6</t>
+          <t>-22,29; -2,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,64; -29,15</t>
+          <t>-45,3; -29,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 21,23</t>
+          <t>4,58; 20,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 8,43</t>
+          <t>-9,58; 7,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -32,67</t>
+          <t>-42,45; -29,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,34</t>
+          <t>1,65; 14,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 1,38</t>
+          <t>-12,41; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-44,34; -32,95</t>
+          <t>-41,78; -31,63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-81,5%</t>
+          <t>-80,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-79,64%</t>
+          <t>-73,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-80,29%</t>
+          <t>-76,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 28,12</t>
+          <t>-15,53; 28,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,47; -3,62</t>
+          <t>-44,41; -6,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,29; -70,57</t>
+          <t>-88,21; -68,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,37; 48,24</t>
+          <t>8,92; 48,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 18,82</t>
+          <t>-18,21; 17,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,74; -71,27</t>
+          <t>-79,62; -65,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 32,14</t>
+          <t>3,23; 33,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 3,11</t>
+          <t>-24,15; 3,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,47; -74,15</t>
+          <t>-81,37; -69,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-21,4</t>
+          <t>-20,66</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-31,27</t>
+          <t>-29,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-27,16</t>
+          <t>-25,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 20,9</t>
+          <t>-3,51; 21,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,77; 40,81</t>
+          <t>17,7; 41,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -11,69</t>
+          <t>-29,67; -9,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,19; 31,7</t>
+          <t>10,25; 31,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,57; 35,37</t>
+          <t>13,82; 36,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,77; -23,6</t>
+          <t>-37,94; -21,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,68; 23,24</t>
+          <t>7,42; 23,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,0; 34,8</t>
+          <t>18,68; 34,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-33,77; -21,39</t>
+          <t>-32,42; -19,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-72,45%</t>
+          <t>-69,96%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-86,75%</t>
+          <t>-81,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-81,54%</t>
+          <t>-77,12%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 90,24</t>
+          <t>-10,21; 96,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>42,79; 179,13</t>
+          <t>47,54; 187,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,42; -49,01</t>
+          <t>-82,14; -46,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,09; 102,2</t>
+          <t>25,09; 106,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,19; 120,55</t>
+          <t>31,72; 121,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-93,74; -77,85</t>
+          <t>-88,72; -71,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,31; 80,1</t>
+          <t>19,57; 80,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>48,12; 123,54</t>
+          <t>49,54; 120,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-88,01; -72,99</t>
+          <t>-84,14; -66,65</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-31,8</t>
+          <t>-31,38</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-28,28</t>
+          <t>-28,12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-29,99</t>
+          <t>-29,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 18,52</t>
+          <t>-3,45; 17,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 7,37</t>
+          <t>-13,82; 8,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -22,3</t>
+          <t>-39,69; -22,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,08; 28,06</t>
+          <t>7,27; 27,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 11,74</t>
+          <t>-9,44; 11,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-36,39; -19,16</t>
+          <t>-36,15; -20,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,35; 19,42</t>
+          <t>4,99; 19,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 6,79</t>
+          <t>-8,59; 6,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-36,03; -24,08</t>
+          <t>-35,99; -24,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-73,99%</t>
+          <t>-73,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-69,9%</t>
+          <t>-69,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-71,99%</t>
+          <t>-71,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 49,94</t>
+          <t>-7,92; 44,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 19,69</t>
+          <t>-28,81; 21,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -61,0</t>
+          <t>-81,43; -61,73</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,22; 83,83</t>
+          <t>16,07; 81,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 32,48</t>
+          <t>-20,93; 33,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,44; -56,38</t>
+          <t>-78,09; -58,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,23; 52,12</t>
+          <t>10,89; 51,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 17,61</t>
+          <t>-18,93; 17,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,24; -63,74</t>
+          <t>-77,96; -64,14</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-31,81</t>
+          <t>-31,62</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-24,51</t>
+          <t>-46,89</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-27,28</t>
+          <t>-40,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>18,3; 33,12</t>
+          <t>18,82; 33,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 14,56</t>
+          <t>-0,6; 16,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -26,12</t>
+          <t>-37,09; -26,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,9; 19,07</t>
+          <t>6,22; 18,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 4,51</t>
+          <t>-8,45; 4,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 12,42</t>
+          <t>-51,52; -42,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,73; 23,34</t>
+          <t>13,76; 23,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 7,4</t>
+          <t>-2,88; 7,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 2,4</t>
+          <t>-43,79; -36,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-91,27%</t>
+          <t>-90,73%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-47,28%</t>
+          <t>-90,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-61,56%</t>
+          <t>-90,71%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>46,33; 108,37</t>
+          <t>49,37; 109,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 47,2</t>
+          <t>-1,63; 49,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-94,94; -85,51</t>
+          <t>-94,52; -85,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,3; 39,66</t>
+          <t>11,16; 38,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 9,38</t>
+          <t>-15,74; 10,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-92,85; 24,47</t>
+          <t>-92,63; -87,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,69; 56,6</t>
+          <t>29,4; 56,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 17,76</t>
+          <t>-6,27; 17,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,6; 5,28</t>
+          <t>-92,67; -87,98</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-20,26</t>
+          <t>-15,29</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-14,32</t>
+          <t>-13,78</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-18,46</t>
+          <t>-14,72</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,23; 19,36</t>
+          <t>7,49; 20,95</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,37; 25,78</t>
+          <t>12,99; 25,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -13,34</t>
+          <t>-20,27; -10,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,6; 26,69</t>
+          <t>14,2; 25,72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,55; 23,69</t>
+          <t>11,59; 24,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -9,29</t>
+          <t>-18,34; -8,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,97; 21,64</t>
+          <t>12,98; 22,05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,99</t>
+          <t>13,94; 22,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -13,54</t>
+          <t>-18,61; -11,08</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-61,09%</t>
+          <t>-46,11%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-34,87%</t>
+          <t>-33,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-49,37%</t>
+          <t>-39,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>16,46; 63,63</t>
+          <t>21,19; 70,83</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>33,92; 87,09</t>
+          <t>36,12; 85,74</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-82,67; -43,61</t>
+          <t>-55,48; -33,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32,47; 71,04</t>
+          <t>32,4; 67,9</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26,47; 63,2</t>
+          <t>25,73; 62,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,46; -24,62</t>
+          <t>-41,91; -21,84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,54; 61,58</t>
+          <t>32,59; 63,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>35,66; 66,34</t>
+          <t>35,32; 64,65</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-68,32; -37,5</t>
+          <t>-46,94; -31,69</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-29,23</t>
+          <t>-28,09</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-29,38</t>
+          <t>-33,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-29,57</t>
+          <t>-30,98</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,38</t>
+          <t>9,5; 15,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,35</t>
+          <t>4,16; 10,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-31,87; -26,56</t>
+          <t>-30,72; -25,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,2</t>
+          <t>12,7; 18,32</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,07</t>
+          <t>2,49; 8,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -13,19</t>
+          <t>-35,41; -30,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,18</t>
+          <t>11,99; 16,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,18</t>
+          <t>4,15; 8,5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -21,31</t>
+          <t>-32,67; -29,27</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-79,08%</t>
+          <t>-76,01%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-63,86%</t>
+          <t>-72,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-70,56%</t>
+          <t>-73,94%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>24,23; 43,04</t>
+          <t>25,1; 44,59</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,93; 28,89</t>
+          <t>10,56; 28,91</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-83,61; -75,7</t>
+          <t>-79,08; -73,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26,64; 41,24</t>
+          <t>26,82; 41,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,1</t>
+          <t>5,18; 18,58</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -29,03</t>
+          <t>-74,48; -69,47</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,2; 40,1</t>
+          <t>27,87; 39,88</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,52; 20,02</t>
+          <t>9,74; 20,92</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-77,41; -50,83</t>
+          <t>-75,69; -71,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
